--- a/web/files/九龙-启德-Monaco 第1期.xlsx
+++ b/web/files/九龙-启德-Monaco 第1期.xlsx
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -9994,7 +9994,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>8584000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>24249</v>
+        <v>24317</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>8584000</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>24249</v>
+        <v>24317</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
           <t>B | 678呎 (3房)
 $2017万
 $29,752/呎
-(26年-08月-31日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -27023,9 +27023,9 @@
       </c>
       <c r="G30" s="20" t="inlineStr">
         <is>
-          <t>F | 354呎 (1房)
+          <t>F | 353呎 (1房)
 $858万
-$24,249/呎
+$24,317/呎
 (21年-02月-11日)</t>
         </is>
       </c>

--- a/web/files/九龙-启德-Monaco 第1期.xlsx
+++ b/web/files/九龙-启德-Monaco 第1期.xlsx
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>9081000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>25725</v>
+        <v>25653</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>9081000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>25725</v>
+        <v>25653</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>9064000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>25677</v>
+        <v>25605</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>9064000</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>25677</v>
+        <v>25605</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>8668000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>24555</v>
+        <v>24486</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>8668000</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>24555</v>
+        <v>24486</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>19580000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>25729</v>
+        <v>25696</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>19580000</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>25729</v>
+        <v>25696</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>20245000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>26603</v>
+        <v>26568</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>20245000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>26603</v>
+        <v>26568</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>8983000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>25448</v>
+        <v>25376</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>8983000</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>25448</v>
+        <v>25376</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>18887000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>24819</v>
+        <v>24786</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>18887000</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>24819</v>
+        <v>24786</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>8591000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>24337</v>
+        <v>24268</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>8591000</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>24337</v>
+        <v>24268</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>19890000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>26137</v>
+        <v>26102</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>19890000</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>26137</v>
+        <v>26102</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>8889000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>25181</v>
+        <v>25110</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>8889000</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>25181</v>
+        <v>25110</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>19601000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>25757</v>
+        <v>25723</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>19601000</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>25757</v>
+        <v>25723</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>8489000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>24048</v>
+        <v>23980</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>8489000</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>24048</v>
+        <v>23980</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>18607000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>24451</v>
+        <v>24419</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>18607000</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>24451</v>
+        <v>24419</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>8823000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>24994</v>
+        <v>24924</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>8823000</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>24994</v>
+        <v>24924</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>18495000</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>24304</v>
+        <v>24272</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>18495000</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>24304</v>
+        <v>24272</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>8321000</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>23572</v>
+        <v>23506</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>8321000</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>23572</v>
+        <v>23506</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>18649000</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>24506</v>
+        <v>24474</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>18649000</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>24506</v>
+        <v>24474</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>17426000</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>22899</v>
+        <v>22869</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>17426000</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>22899</v>
+        <v>22869</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>17561000</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>23076</v>
+        <v>23046</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>17561000</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>23076</v>
+        <v>23046</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>17617000</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>23150</v>
+        <v>23119</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>17617000</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>23150</v>
+        <v>23119</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>8584000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>24317</v>
+        <v>24249</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>8584000</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>24317</v>
+        <v>24249</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>17728000</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>23296</v>
+        <v>23265</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>17728000</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>23296</v>
+        <v>23265</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>18888000</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>24820</v>
+        <v>24787</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>18888000</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>24820</v>
+        <v>24787</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         </is>
       </c>
       <c r="E189" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>7194000</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>25785</v>
+        <v>25693</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>7194000</v>
       </c>
       <c r="L189" s="5" t="n">
-        <v>25785</v>
+        <v>25693</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>7182000</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>25742</v>
+        <v>25650</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>7182000</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>25742</v>
+        <v>25650</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>7039000</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>25229</v>
+        <v>25139</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>7039000</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>25229</v>
+        <v>25139</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         </is>
       </c>
       <c r="E217" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>6875000</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>24642</v>
+        <v>24554</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>6875000</v>
       </c>
       <c r="L217" s="5" t="n">
-        <v>24642</v>
+        <v>24554</v>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>7070000</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>25341</v>
+        <v>25250</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>7070000</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>25341</v>
+        <v>25250</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>7174000</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>25713</v>
+        <v>25621</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>7174000</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>25713</v>
+        <v>25621</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         </is>
       </c>
       <c r="E252" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>6721000</v>
       </c>
       <c r="I252" s="5" t="n">
-        <v>24090</v>
+        <v>24004</v>
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>6721000</v>
       </c>
       <c r="L252" s="5" t="n">
-        <v>24090</v>
+        <v>24004</v>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="E259" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>7087000</v>
       </c>
       <c r="I259" s="5" t="n">
-        <v>25401</v>
+        <v>25311</v>
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>7087000</v>
       </c>
       <c r="L259" s="5" t="n">
-        <v>25401</v>
+        <v>25311</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         </is>
       </c>
       <c r="E280" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>6770000</v>
       </c>
       <c r="I280" s="5" t="n">
-        <v>24265</v>
+        <v>24179</v>
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>6770000</v>
       </c>
       <c r="L280" s="5" t="n">
-        <v>24265</v>
+        <v>24179</v>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="E308" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F308" s="3" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>6754000</v>
       </c>
       <c r="I308" s="5" t="n">
-        <v>24208</v>
+        <v>24121</v>
       </c>
       <c r="J308" s="3" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>6754000</v>
       </c>
       <c r="L308" s="5" t="n">
-        <v>24208</v>
+        <v>24121</v>
       </c>
       <c r="M308" s="3" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         </is>
       </c>
       <c r="E315" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F315" s="3" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>6734000</v>
       </c>
       <c r="I315" s="5" t="n">
-        <v>24136</v>
+        <v>24050</v>
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>6734000</v>
       </c>
       <c r="L315" s="5" t="n">
-        <v>24136</v>
+        <v>24050</v>
       </c>
       <c r="M315" s="3" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         </is>
       </c>
       <c r="E322" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>6694000</v>
       </c>
       <c r="I322" s="5" t="n">
-        <v>23993</v>
+        <v>23907</v>
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>6694000</v>
       </c>
       <c r="L322" s="5" t="n">
-        <v>23993</v>
+        <v>23907</v>
       </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         </is>
       </c>
       <c r="E329" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>6677000</v>
       </c>
       <c r="I329" s="5" t="n">
-        <v>23932</v>
+        <v>23846</v>
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>6677000</v>
       </c>
       <c r="L329" s="5" t="n">
-        <v>23932</v>
+        <v>23846</v>
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         </is>
       </c>
       <c r="E343" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>6357000</v>
       </c>
       <c r="I343" s="5" t="n">
-        <v>22785</v>
+        <v>22704</v>
       </c>
       <c r="J343" s="3" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>6357000</v>
       </c>
       <c r="L343" s="5" t="n">
-        <v>22785</v>
+        <v>22704</v>
       </c>
       <c r="M343" s="3" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="E364" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>6578000</v>
       </c>
       <c r="I364" s="5" t="n">
-        <v>23577</v>
+        <v>23493</v>
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>6578000</v>
       </c>
       <c r="L364" s="5" t="n">
-        <v>23577</v>
+        <v>23493</v>
       </c>
       <c r="M364" s="3" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         </is>
       </c>
       <c r="E378" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>6205000</v>
       </c>
       <c r="I378" s="5" t="n">
-        <v>22240</v>
+        <v>22161</v>
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>6205000</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>22240</v>
+        <v>22161</v>
       </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         </is>
       </c>
       <c r="E385" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>6152000</v>
       </c>
       <c r="I385" s="5" t="n">
-        <v>22050</v>
+        <v>21971</v>
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>6152000</v>
       </c>
       <c r="L385" s="5" t="n">
-        <v>22050</v>
+        <v>21971</v>
       </c>
       <c r="M385" s="3" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         </is>
       </c>
       <c r="E398" s="4" t="n">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>9590000</v>
       </c>
       <c r="I398" s="5" t="n">
-        <v>21217</v>
+        <v>21264</v>
       </c>
       <c r="J398" s="3" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>9590000</v>
       </c>
       <c r="L398" s="5" t="n">
-        <v>21217</v>
+        <v>21264</v>
       </c>
       <c r="M398" s="3" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         </is>
       </c>
       <c r="E399" s="4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F399" s="3" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>5966000</v>
       </c>
       <c r="I399" s="5" t="n">
-        <v>21384</v>
+        <v>21307</v>
       </c>
       <c r="J399" s="3" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>5966000</v>
       </c>
       <c r="L399" s="5" t="n">
-        <v>21384</v>
+        <v>21307</v>
       </c>
       <c r="M399" s="3" t="inlineStr">
         <is>
@@ -25758,9 +25758,9 @@
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>F | 353呎 (1房)
+          <t>F | 354呎 (1房)
 $908万
-$25,725/呎
+$25,653/呎
 (21年-02月-17日)</t>
         </is>
       </c>
@@ -25923,9 +25923,9 @@
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>F | 353呎 (1房)
+          <t>F | 354呎 (1房)
 $906万
-$25,677/呎
+$25,605/呎
 (25年-05月-02日)</t>
         </is>
       </c>
@@ -25978,9 +25978,9 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>F | 353呎 (1房)
+          <t>F | 354呎 (1房)
 $867万
-$24,555/呎
+$24,486/呎
 (21年-02月-17日)</t>
         </is>
       </c>
@@ -25993,9 +25993,9 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $1958万
-$25,729/呎
+$25,696/呎
 (21年-02月-17日)</t>
         </is>
       </c>
@@ -26103,9 +26103,9 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $2024万
-$26,603/呎
+$26,568/呎
 (21年-02月-17日)</t>
         </is>
       </c>
@@ -26158,9 +26158,9 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $1889万
-$24,819/呎
+$24,786/呎
 (21年-02月-10日)</t>
         </is>
       </c>
@@ -26198,9 +26198,9 @@
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>F | 353呎 (1房)
+          <t>F | 354呎 (1房)
 $898万
-$25,448/呎
+$25,376/呎
 (21年-02月-17日)</t>
         </is>
       </c>
@@ -26213,9 +26213,9 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $1989万
-$26,137/呎
+$26,102/呎
 (21年-02月-17日)</t>
         </is>
       </c>
@@ -26253,9 +26253,9 @@
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>F | 353呎 (1房)
+          <t>F | 354呎 (1房)
 $859万
-$24,337/呎
+$24,268/呎
 (21年-01月-21日)</t>
         </is>
       </c>
@@ -26268,9 +26268,9 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $1960万
-$25,757/呎
+$25,723/呎
 (21年-02月-10日)</t>
         </is>
       </c>
@@ -26308,9 +26308,9 @@
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>F | 353呎 (1房)
+          <t>F | 354呎 (1房)
 $889万
-$25,181/呎
+$25,110/呎
 (21年-02月-09日)</t>
         </is>
       </c>
@@ -26418,9 +26418,9 @@
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>F | 353呎 (1房)
+          <t>F | 354呎 (1房)
 $849万
-$24,048/呎
+$23,980/呎
 (21年-02月-09日)</t>
         </is>
       </c>
@@ -26433,9 +26433,9 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $1861万
-$24,451/呎
+$24,419/呎
 (21年-02月-05日)</t>
         </is>
       </c>
@@ -26528,9 +26528,9 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>F | 353呎 (1房)
+          <t>F | 354呎 (1房)
 $882万
-$24,994/呎
+$24,924/呎
 (21年-02月-09日)</t>
         </is>
       </c>
@@ -26543,9 +26543,9 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $1850万
-$24,304/呎
+$24,272/呎
 (21年-02月-10日)</t>
         </is>
       </c>
@@ -26653,9 +26653,9 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $1865万
-$24,506/呎
+$24,474/呎
 (21年-02月-10日)</t>
         </is>
       </c>
@@ -26693,9 +26693,9 @@
       </c>
       <c r="G24" s="20" t="inlineStr">
         <is>
-          <t>F | 353呎 (1房)
+          <t>F | 354呎 (1房)
 $832万
-$23,572/呎
+$23,506/呎
 (21年-02月-05日)</t>
         </is>
       </c>
@@ -26763,9 +26763,9 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $1743万
-$22,899/呎
+$22,869/呎
 (21年-02月-05日)</t>
         </is>
       </c>
@@ -26873,9 +26873,9 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $1756万
-$23,076/呎
+$23,046/呎
 (21年-01月-17日)</t>
         </is>
       </c>
@@ -26928,9 +26928,9 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $1762万
-$23,150/呎
+$23,119/呎
 (21年-01月-17日)</t>
         </is>
       </c>
@@ -27023,9 +27023,9 @@
       </c>
       <c r="G30" s="20" t="inlineStr">
         <is>
-          <t>F | 353呎 (1房)
+          <t>F | 354呎 (1房)
 $858万
-$24,317/呎
+$24,249/呎
 (21年-02月-11日)</t>
         </is>
       </c>
@@ -27093,9 +27093,9 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $1773万
-$23,296/呎
+$23,265/呎
 (21年-01月-17日)</t>
         </is>
       </c>
@@ -27203,9 +27203,9 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>A | 761呎 (3房)
+          <t>A | 762呎 (3房)
 $1889万
-$24,820/呎
+$24,787/呎
 (21年-02月-16日)</t>
         </is>
       </c>
@@ -27494,9 +27494,9 @@
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $719万
-$25,785/呎
+$25,693/呎
 (21年-02月-25日)</t>
         </is>
       </c>
@@ -27557,9 +27557,9 @@
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $718万
-$25,742/呎
+$25,650/呎
 (21年-02月-25日)</t>
         </is>
       </c>
@@ -27620,9 +27620,9 @@
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $704万
-$25,229/呎
+$25,139/呎
 (21年-02月-10日)</t>
         </is>
       </c>
@@ -27746,9 +27746,9 @@
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $688万
-$24,642/呎
+$24,554/呎
 (21年-02月-25日)</t>
         </is>
       </c>
@@ -27809,9 +27809,9 @@
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $707万
-$25,341/呎
+$25,250/呎
 (21年-02月-09日)</t>
         </is>
       </c>
@@ -27872,9 +27872,9 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $717万
-$25,713/呎
+$25,621/呎
 (21年-02月-25日)</t>
         </is>
       </c>
@@ -28061,9 +28061,9 @@
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $672万
-$24,090/呎
+$24,004/呎
 (21年-01月-21日)</t>
         </is>
       </c>
@@ -28124,9 +28124,9 @@
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $709万
-$25,401/呎
+$25,311/呎
 (21年-02月-25日)</t>
         </is>
       </c>
@@ -28313,9 +28313,9 @@
       </c>
       <c r="G18" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $677万
-$24,265/呎
+$24,179/呎
 (21年-01月-21日)</t>
         </is>
       </c>
@@ -28565,9 +28565,9 @@
       </c>
       <c r="G22" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $675万
-$24,208/呎
+$24,121/呎
 (21年-02月-05日)</t>
         </is>
       </c>
@@ -28628,9 +28628,9 @@
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $673万
-$24,136/呎
+$24,050/呎
 (21年-02月-05日)</t>
         </is>
       </c>
@@ -28691,9 +28691,9 @@
       </c>
       <c r="G24" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $669万
-$23,993/呎
+$23,907/呎
 (21年-02月-05日)</t>
         </is>
       </c>
@@ -28754,9 +28754,9 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $668万
-$23,932/呎
+$23,846/呎
 (21年-02月-03日)</t>
         </is>
       </c>
@@ -28880,9 +28880,9 @@
       </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $636万
-$22,785/呎
+$22,704/呎
 (21年-02月-11日)</t>
         </is>
       </c>
@@ -29069,9 +29069,9 @@
       </c>
       <c r="G30" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $658万
-$23,577/呎
+$23,493/呎
 (21年-02月-10日)</t>
         </is>
       </c>
@@ -29195,9 +29195,9 @@
       </c>
       <c r="G32" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $620万
-$22,240/呎
+$22,161/呎
 (21年-02月-10日)</t>
         </is>
       </c>
@@ -29258,9 +29258,9 @@
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $615万
-$22,050/呎
+$21,971/呎
 (21年-01月-17日)</t>
         </is>
       </c>
@@ -29363,17 +29363,17 @@
       </c>
       <c r="G35" s="20" t="inlineStr">
         <is>
-          <t>F | 279呎 (开放式)
+          <t>F | 280呎 (开放式)
 $597万
-$21,384/呎
+$21,307/呎
 (21年-02月-11日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
-          <t>G | 452呎 (2房)
+          <t>G | 451呎 (2房)
 $959万
-$21,217/呎
+$21,264/呎
 (21年-02月-11日)</t>
         </is>
       </c>
